--- a/bin/excelutility/Webtabledata.xlsx
+++ b/bin/excelutility/Webtabledata.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sd47860\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dubey\OneDrive\Documents\GitHub\18october_framework\src\main\pages\excelutility\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34816968-8B8C-4837-B720-A50943A9967C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="7032"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,18 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="4">
   <si>
     <t>shivam dubey</t>
-  </si>
-  <si>
-    <t>sonu kumar</t>
-  </si>
-  <si>
-    <t>salman khan</t>
-  </si>
-  <si>
-    <t>sharukh khan</t>
   </si>
   <si>
     <t>dubeyshivam890@gmail.com</t>
@@ -46,29 +38,11 @@
   <si>
     <t>salmankhan4@gmail.com</t>
   </si>
-  <si>
-    <t>ravi45@gmail.com</t>
-  </si>
-  <si>
-    <t>atul353535@gmail.com</t>
-  </si>
-  <si>
-    <t>ajay4545@gmail.com</t>
-  </si>
-  <si>
-    <t>ravi kumar</t>
-  </si>
-  <si>
-    <t>atul gogal</t>
-  </si>
-  <si>
-    <t>ajay bhai</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -390,79 +364,653 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B79"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+    <col min="2" max="2" width="26.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1"/>
-    <hyperlink ref="B2" r:id="rId2"/>
-    <hyperlink ref="B3" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" r:id="rId5"/>
-    <hyperlink ref="B7" r:id="rId6"/>
-    <hyperlink ref="B4" r:id="rId7"/>
+    <hyperlink ref="B1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B5:B79" r:id="rId5" display="salmankhan4@gmail.com" xr:uid="{E86C2957-CD7E-47B9-9734-AAB65A6EB0F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
